--- a/Result/checksun/橡膠工業.xlsx
+++ b/Result/checksun/橡膠工業.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1897,11 +1897,15 @@
           <t>31.16</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>31.38</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>31.75</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>31.38</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>31.75</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2654,7 +2658,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2669,7 +2673,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -2679,12 +2683,12 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2883,11 +2887,15 @@
           <t>31.125</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>31.41</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>31.76</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>31.41</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>31.76</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3640,7 +3648,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3655,7 +3663,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -3665,12 +3673,12 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3869,11 +3877,15 @@
           <t>31.115</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>31.45</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>31.79</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>31.45</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>31.79</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4626,7 +4638,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4641,7 +4653,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -4651,12 +4663,12 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4855,11 +4867,15 @@
           <t>31.125</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>31.8</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>31.52</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>31.8</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5612,7 +5628,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5627,7 +5643,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -5637,12 +5653,12 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5841,11 +5857,15 @@
           <t>31.195</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>31.84</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>31.61</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>31.84</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6598,7 +6618,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6613,22 +6633,22 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6827,11 +6847,15 @@
           <t>31.255</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>31.87</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>31.7</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>31.87</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7584,7 +7608,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7599,22 +7623,22 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7813,11 +7837,15 @@
           <t>31.375</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>31.91</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>31.79</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>31.91</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8570,7 +8598,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8585,22 +8613,22 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8799,11 +8827,15 @@
           <t>31.44</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>31.93</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>31.84</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>31.93</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9556,7 +9588,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9571,22 +9603,22 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9785,11 +9817,15 @@
           <t>31.52</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>31.92</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>31.96</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>31.92</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>31.96</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10542,37 +10578,37 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10771,11 +10807,15 @@
           <t>89.75</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>89.47</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>88.69</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>89.47</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>88.69</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -10891,7 +10931,7 @@
       </c>
       <c r="DQ11" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR11" t="inlineStr">
@@ -11528,37 +11568,37 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11757,11 +11797,15 @@
           <t>89.61</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>89.43000000000001</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>88.64</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>89.43</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>88.64</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -11877,7 +11921,7 @@
       </c>
       <c r="DQ12" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR12" t="inlineStr">
@@ -12514,37 +12558,37 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12743,11 +12787,15 @@
           <t>89.47</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>88.59999999999999</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -12863,7 +12911,7 @@
       </c>
       <c r="DQ13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR13" t="inlineStr">
@@ -13500,37 +13548,37 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13729,11 +13777,15 @@
           <t>89.35999999999999</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>89.36</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>88.56</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>89.36</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>88.56</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -13849,7 +13901,7 @@
       </c>
       <c r="DQ14" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR14" t="inlineStr">
@@ -14486,37 +14538,37 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14715,11 +14767,15 @@
           <t>89.31</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>89.33</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>88.52</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>89.33</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>88.52</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -14835,7 +14891,7 @@
       </c>
       <c r="DQ15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR15" t="inlineStr">
@@ -15472,37 +15528,37 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15701,11 +15757,15 @@
           <t>89.23</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>89.31999999999999</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>88.51000000000001</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>89.32</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>88.51</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -15821,7 +15881,7 @@
       </c>
       <c r="DQ16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR16" t="inlineStr">
@@ -16458,37 +16518,37 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16687,11 +16747,15 @@
           <t>89.21000000000001</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>88.5</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -16807,7 +16871,7 @@
       </c>
       <c r="DQ17" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR17" t="inlineStr">
@@ -17444,7 +17508,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17459,22 +17523,22 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17673,11 +17737,15 @@
           <t>89.22</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>89.23</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>88.48</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>89.23</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>88.48</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18430,7 +18498,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18445,22 +18513,22 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18659,11 +18727,15 @@
           <t>89.24999999999999</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>89.17</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>88.47</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>89.17</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>88.47</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19401,52 +19473,52 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -19645,11 +19717,15 @@
           <t>14.64</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>14.66</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>14.72</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>14.66</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20387,52 +20463,52 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT21" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -20631,11 +20707,15 @@
           <t>14.675</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>14.66</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>14.74</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>14.66</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21368,57 +21448,57 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AS22" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT22" t="inlineStr">
+      <c r="AY22" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -21617,11 +21697,15 @@
           <t>14.705</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>14.76</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>14.66</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>14.76</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>14.66</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22354,57 +22438,57 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -22603,11 +22687,15 @@
           <t>14.74</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>14.78</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>14.67</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>14.78</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>14.67</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23335,62 +23423,62 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AS24" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT24" t="inlineStr">
+      <c r="AY24" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -23589,11 +23677,15 @@
           <t>14.775</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>14.67</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>14.67</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24346,7 +24438,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -24361,22 +24453,22 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -24575,11 +24667,15 @@
           <t>14.75</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>14.67</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>14.79</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>14.67</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25332,7 +25428,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -25347,22 +25443,22 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -25561,11 +25657,15 @@
           <t>14.755</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>14.67</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>14.79</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>14.67</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26318,7 +26418,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -26333,22 +26433,22 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
@@ -26547,11 +26647,15 @@
           <t>14.77</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>14.66</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>14.79</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>14.66</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27304,7 +27408,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -27319,22 +27423,22 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
@@ -27533,11 +27637,15 @@
           <t>14.785</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>14.66</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>14.79</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>14.66</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28290,7 +28398,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -28305,7 +28413,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
@@ -28315,12 +28423,12 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28519,11 +28627,15 @@
           <t>28.605</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>28.76</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>28.98</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>28.76</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>28.98</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29276,7 +29388,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -29291,7 +29403,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -29301,12 +29413,12 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29505,11 +29617,15 @@
           <t>28.595</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>28.87</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>28.97</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>28.87</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>28.97</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30262,7 +30378,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -30277,22 +30393,22 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30491,11 +30607,15 @@
           <t>28.535</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>28.98</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>28.97</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>28.98</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>28.97</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31248,7 +31368,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -31263,22 +31383,22 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31477,11 +31597,15 @@
           <t>28.45</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>29.07</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>28.94</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>29.07</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>28.94</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32234,7 +32358,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -32249,22 +32373,22 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32463,11 +32587,15 @@
           <t>28.54</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>29.18</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>28.94</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>29.18</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>28.94</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33220,7 +33348,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -33235,22 +33363,22 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33449,11 +33577,15 @@
           <t>28.57</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>28.93</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>28.93</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34206,7 +34338,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -34221,22 +34353,22 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34435,11 +34567,15 @@
           <t>28.645</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>29.35</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>28.93</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>29.35</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>28.93</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35192,7 +35328,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -35207,22 +35343,22 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35421,11 +35557,15 @@
           <t>28.7</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>29.42</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>28.92</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>29.42</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>28.92</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36178,7 +36318,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -36193,22 +36333,22 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36407,11 +36547,15 @@
           <t>28.715</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>29.49</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>28.92</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>29.49</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>28.92</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
@@ -37154,7 +37298,7 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
@@ -37164,12 +37308,12 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -37179,22 +37323,22 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -37393,11 +37537,15 @@
           <t>26.975</t>
         </is>
       </c>
-      <c r="CQ38" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="CR38" t="n">
-        <v>26.36</v>
+      <c r="CQ38" t="inlineStr">
+        <is>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>26.36</t>
+        </is>
       </c>
       <c r="CS38" t="inlineStr">
         <is>
@@ -38140,7 +38288,7 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
@@ -38150,7 +38298,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -38160,27 +38308,27 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -38379,11 +38527,15 @@
           <t>26.94</t>
         </is>
       </c>
-      <c r="CQ39" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>26.33</v>
+      <c r="CQ39" t="inlineStr">
+        <is>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>26.33</t>
+        </is>
       </c>
       <c r="CS39" t="inlineStr">
         <is>
@@ -39126,7 +39278,7 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
@@ -39136,7 +39288,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -39151,22 +39303,22 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -39365,11 +39517,15 @@
           <t>26.915</t>
         </is>
       </c>
-      <c r="CQ40" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>26.32</v>
+      <c r="CQ40" t="inlineStr">
+        <is>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>26.32</t>
+        </is>
       </c>
       <c r="CS40" t="inlineStr">
         <is>
@@ -40112,7 +40268,7 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
@@ -40122,7 +40278,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -40132,27 +40288,27 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -40351,11 +40507,15 @@
           <t>26.875</t>
         </is>
       </c>
-      <c r="CQ41" t="n">
-        <v>26.85</v>
-      </c>
-      <c r="CR41" t="n">
-        <v>26.29</v>
+      <c r="CQ41" t="inlineStr">
+        <is>
+          <t>26.85</t>
+        </is>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>26.29</t>
+        </is>
       </c>
       <c r="CS41" t="inlineStr">
         <is>
@@ -41093,12 +41253,12 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
@@ -41108,7 +41268,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -41118,27 +41278,27 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -41337,11 +41497,15 @@
           <t>26.87</t>
         </is>
       </c>
-      <c r="CQ42" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>26.27</v>
+      <c r="CQ42" t="inlineStr">
+        <is>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>26.27</t>
+        </is>
       </c>
       <c r="CS42" t="inlineStr">
         <is>
@@ -42079,12 +42243,12 @@
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
@@ -42094,37 +42258,37 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -42323,11 +42487,15 @@
           <t>26.88</t>
         </is>
       </c>
-      <c r="CQ43" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>26.25</v>
+      <c r="CQ43" t="inlineStr">
+        <is>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>26.25</t>
+        </is>
       </c>
       <c r="CS43" t="inlineStr">
         <is>
@@ -43060,17 +43228,17 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
@@ -43080,37 +43248,37 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -43309,11 +43477,15 @@
           <t>26.88</t>
         </is>
       </c>
-      <c r="CQ44" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>26.23</v>
+      <c r="CQ44" t="inlineStr">
+        <is>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>26.23</t>
+        </is>
       </c>
       <c r="CS44" t="inlineStr">
         <is>
@@ -44046,17 +44218,17 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
@@ -44066,37 +44238,37 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW45" t="inlineStr">
+      <c r="AX45" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
@@ -44295,11 +44467,15 @@
           <t>26.855</t>
         </is>
       </c>
-      <c r="CQ45" t="n">
-        <v>26.85</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>26.21</v>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>26.85</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>26.21</t>
+        </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
@@ -45027,62 +45203,62 @@
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV46" t="inlineStr">
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -45281,11 +45457,15 @@
           <t>26.8</t>
         </is>
       </c>
-      <c r="CQ46" t="n">
-        <v>26.83</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>26.19</v>
+      <c r="CQ46" t="inlineStr">
+        <is>
+          <t>26.83</t>
+        </is>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>26.19</t>
+        </is>
       </c>
       <c r="CS46" t="inlineStr">
         <is>
@@ -46038,7 +46218,7 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
@@ -46053,7 +46233,7 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
@@ -46068,7 +46248,7 @@
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
@@ -46267,11 +46447,15 @@
           <t>16.58</t>
         </is>
       </c>
-      <c r="CQ47" t="n">
-        <v>16.72</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>17.36</v>
+      <c r="CQ47" t="inlineStr">
+        <is>
+          <t>16.72</t>
+        </is>
+      </c>
+      <c r="CR47" t="inlineStr">
+        <is>
+          <t>17.36</t>
+        </is>
       </c>
       <c r="CS47" t="inlineStr">
         <is>
@@ -47024,7 +47208,7 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
@@ -47039,7 +47223,7 @@
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
@@ -47054,7 +47238,7 @@
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
@@ -47253,11 +47437,15 @@
           <t>16.565</t>
         </is>
       </c>
-      <c r="CQ48" t="n">
-        <v>16.76</v>
-      </c>
-      <c r="CR48" t="n">
-        <v>17.38</v>
+      <c r="CQ48" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="CR48" t="inlineStr">
+        <is>
+          <t>17.38</t>
+        </is>
       </c>
       <c r="CS48" t="inlineStr">
         <is>
@@ -48010,7 +48198,7 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
@@ -48025,7 +48213,7 @@
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
@@ -48040,7 +48228,7 @@
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
@@ -48239,11 +48427,15 @@
           <t>16.56</t>
         </is>
       </c>
-      <c r="CQ49" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="CR49" t="n">
-        <v>17.4</v>
+      <c r="CQ49" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
+      </c>
+      <c r="CR49" t="inlineStr">
+        <is>
+          <t>17.4</t>
+        </is>
       </c>
       <c r="CS49" t="inlineStr">
         <is>
@@ -48996,7 +49188,7 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
@@ -49011,7 +49203,7 @@
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
@@ -49026,7 +49218,7 @@
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
@@ -49225,11 +49417,15 @@
           <t>16.55</t>
         </is>
       </c>
-      <c r="CQ50" t="n">
-        <v>16.82</v>
-      </c>
-      <c r="CR50" t="n">
-        <v>17.43</v>
+      <c r="CQ50" t="inlineStr">
+        <is>
+          <t>16.82</t>
+        </is>
+      </c>
+      <c r="CR50" t="inlineStr">
+        <is>
+          <t>17.43</t>
+        </is>
       </c>
       <c r="CS50" t="inlineStr">
         <is>
@@ -49982,7 +50178,7 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
@@ -49997,7 +50193,7 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
@@ -50012,7 +50208,7 @@
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
@@ -50211,11 +50407,15 @@
           <t>16.575</t>
         </is>
       </c>
-      <c r="CQ51" t="n">
-        <v>16.84</v>
-      </c>
-      <c r="CR51" t="n">
-        <v>17.46</v>
+      <c r="CQ51" t="inlineStr">
+        <is>
+          <t>16.84</t>
+        </is>
+      </c>
+      <c r="CR51" t="inlineStr">
+        <is>
+          <t>17.46</t>
+        </is>
       </c>
       <c r="CS51" t="inlineStr">
         <is>
@@ -50968,7 +51168,7 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
@@ -50983,7 +51183,7 @@
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
@@ -50998,7 +51198,7 @@
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -51197,11 +51397,15 @@
           <t>16.595</t>
         </is>
       </c>
-      <c r="CQ52" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="CR52" t="n">
-        <v>17.5</v>
+      <c r="CQ52" t="inlineStr">
+        <is>
+          <t>16.86</t>
+        </is>
+      </c>
+      <c r="CR52" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
       </c>
       <c r="CS52" t="inlineStr">
         <is>
@@ -51954,7 +52158,7 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
@@ -51969,7 +52173,7 @@
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
@@ -51979,12 +52183,12 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
@@ -52183,11 +52387,15 @@
           <t>16.635</t>
         </is>
       </c>
-      <c r="CQ53" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>17.52</v>
+      <c r="CQ53" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="CR53" t="inlineStr">
+        <is>
+          <t>17.52</t>
+        </is>
       </c>
       <c r="CS53" t="inlineStr">
         <is>
@@ -52940,7 +53148,7 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
@@ -52955,7 +53163,7 @@
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
@@ -52965,12 +53173,12 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
@@ -53169,11 +53377,15 @@
           <t>16.685</t>
         </is>
       </c>
-      <c r="CQ54" t="n">
-        <v>16.93</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>17.54</v>
+      <c r="CQ54" t="inlineStr">
+        <is>
+          <t>16.93</t>
+        </is>
+      </c>
+      <c r="CR54" t="inlineStr">
+        <is>
+          <t>17.54</t>
+        </is>
       </c>
       <c r="CS54" t="inlineStr">
         <is>
@@ -53926,7 +54138,7 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
@@ -53941,7 +54153,7 @@
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
@@ -53951,12 +54163,12 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
@@ -54155,11 +54367,15 @@
           <t>16.72</t>
         </is>
       </c>
-      <c r="CQ55" t="n">
-        <v>16.98</v>
-      </c>
-      <c r="CR55" t="n">
-        <v>17.56</v>
+      <c r="CQ55" t="inlineStr">
+        <is>
+          <t>16.98</t>
+        </is>
+      </c>
+      <c r="CR55" t="inlineStr">
+        <is>
+          <t>17.56</t>
+        </is>
       </c>
       <c r="CS55" t="inlineStr">
         <is>
@@ -54912,7 +55128,7 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
@@ -54927,7 +55143,7 @@
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
@@ -54937,12 +55153,12 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
@@ -55141,11 +55357,15 @@
           <t>30.21</t>
         </is>
       </c>
-      <c r="CQ56" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="CR56" t="n">
-        <v>30.75</v>
+      <c r="CQ56" t="inlineStr">
+        <is>
+          <t>30.34</t>
+        </is>
+      </c>
+      <c r="CR56" t="inlineStr">
+        <is>
+          <t>30.75</t>
+        </is>
       </c>
       <c r="CS56" t="inlineStr">
         <is>
@@ -55898,7 +56118,7 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
@@ -55913,7 +56133,7 @@
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
@@ -55923,12 +56143,12 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -56127,11 +56347,15 @@
           <t>30.155</t>
         </is>
       </c>
-      <c r="CQ57" t="n">
-        <v>30.37</v>
-      </c>
-      <c r="CR57" t="n">
-        <v>30.76</v>
+      <c r="CQ57" t="inlineStr">
+        <is>
+          <t>30.37</t>
+        </is>
+      </c>
+      <c r="CR57" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
       </c>
       <c r="CS57" t="inlineStr">
         <is>
@@ -56884,7 +57108,7 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
@@ -56899,7 +57123,7 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
@@ -56909,12 +57133,12 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
@@ -57113,11 +57337,15 @@
           <t>30.1</t>
         </is>
       </c>
-      <c r="CQ58" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="CR58" t="n">
-        <v>30.8</v>
+      <c r="CQ58" t="inlineStr">
+        <is>
+          <t>30.4</t>
+        </is>
+      </c>
+      <c r="CR58" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
       </c>
       <c r="CS58" t="inlineStr">
         <is>
@@ -57870,7 +58098,7 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
@@ -57885,7 +58113,7 @@
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
@@ -57895,12 +58123,12 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
@@ -58099,11 +58327,15 @@
           <t>30.05</t>
         </is>
       </c>
-      <c r="CQ59" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="CR59" t="n">
-        <v>30.85</v>
+      <c r="CQ59" t="inlineStr">
+        <is>
+          <t>30.41</t>
+        </is>
+      </c>
+      <c r="CR59" t="inlineStr">
+        <is>
+          <t>30.85</t>
+        </is>
       </c>
       <c r="CS59" t="inlineStr">
         <is>
@@ -58856,7 +59088,7 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
@@ -58871,7 +59103,7 @@
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
@@ -58881,12 +59113,12 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
@@ -59085,11 +59317,15 @@
           <t>30.08</t>
         </is>
       </c>
-      <c r="CQ60" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="CR60" t="n">
-        <v>30.92</v>
+      <c r="CQ60" t="inlineStr">
+        <is>
+          <t>30.44</t>
+        </is>
+      </c>
+      <c r="CR60" t="inlineStr">
+        <is>
+          <t>30.92</t>
+        </is>
       </c>
       <c r="CS60" t="inlineStr">
         <is>
@@ -59842,7 +60078,7 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
@@ -59857,7 +60093,7 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
@@ -59867,12 +60103,12 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
@@ -60071,11 +60307,15 @@
           <t>30.13</t>
         </is>
       </c>
-      <c r="CQ61" t="n">
-        <v>30.48</v>
-      </c>
-      <c r="CR61" t="n">
-        <v>30.99</v>
+      <c r="CQ61" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="CR61" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
       </c>
       <c r="CS61" t="inlineStr">
         <is>
@@ -60828,7 +61068,7 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
@@ -60843,22 +61083,22 @@
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
@@ -61057,11 +61297,15 @@
           <t>30.2</t>
         </is>
       </c>
-      <c r="CQ62" t="n">
-        <v>30.55</v>
-      </c>
-      <c r="CR62" t="n">
-        <v>31.04</v>
+      <c r="CQ62" t="inlineStr">
+        <is>
+          <t>30.55</t>
+        </is>
+      </c>
+      <c r="CR62" t="inlineStr">
+        <is>
+          <t>31.04</t>
+        </is>
       </c>
       <c r="CS62" t="inlineStr">
         <is>
@@ -61814,7 +62058,7 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
@@ -61829,22 +62073,22 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
@@ -62043,11 +62287,15 @@
           <t>30.26</t>
         </is>
       </c>
-      <c r="CQ63" t="n">
-        <v>30.62</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>31.1</v>
+      <c r="CQ63" t="inlineStr">
+        <is>
+          <t>30.62</t>
+        </is>
+      </c>
+      <c r="CR63" t="inlineStr">
+        <is>
+          <t>31.1</t>
+        </is>
       </c>
       <c r="CS63" t="inlineStr">
         <is>
@@ -62800,7 +63048,7 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
@@ -62815,22 +63063,22 @@
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
@@ -63029,11 +63277,15 @@
           <t>30.325</t>
         </is>
       </c>
-      <c r="CQ64" t="n">
-        <v>30.69</v>
-      </c>
-      <c r="CR64" t="n">
-        <v>31.15</v>
+      <c r="CQ64" t="inlineStr">
+        <is>
+          <t>30.69</t>
+        </is>
+      </c>
+      <c r="CR64" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
       </c>
       <c r="CS64" t="inlineStr">
         <is>
@@ -63761,62 +64013,62 @@
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AT65" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
@@ -64015,11 +64267,15 @@
           <t>10.915</t>
         </is>
       </c>
-      <c r="CQ65" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="CR65" t="n">
-        <v>10.37</v>
+      <c r="CQ65" t="inlineStr">
+        <is>
+          <t>10.64</t>
+        </is>
+      </c>
+      <c r="CR65" t="inlineStr">
+        <is>
+          <t>10.37</t>
+        </is>
       </c>
       <c r="CS65" t="inlineStr">
         <is>
@@ -64135,7 +64391,7 @@
       </c>
       <c r="DQ65" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR65" t="inlineStr">
@@ -64747,62 +65003,62 @@
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR66" t="inlineStr">
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS66" t="inlineStr">
+      <c r="AX66" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT66" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV66" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
@@ -65001,11 +65257,15 @@
           <t>10.86</t>
         </is>
       </c>
-      <c r="CQ66" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="CR66" t="n">
-        <v>10.36</v>
+      <c r="CQ66" t="inlineStr">
+        <is>
+          <t>10.62</t>
+        </is>
+      </c>
+      <c r="CR66" t="inlineStr">
+        <is>
+          <t>10.36</t>
+        </is>
       </c>
       <c r="CS66" t="inlineStr">
         <is>
@@ -65121,7 +65381,7 @@
       </c>
       <c r="DQ66" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR66" t="inlineStr">
@@ -65733,62 +65993,62 @@
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR67" t="inlineStr">
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS67" t="inlineStr">
+      <c r="AX67" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT67" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV67" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
@@ -65987,11 +66247,15 @@
           <t>10.79</t>
         </is>
       </c>
-      <c r="CQ67" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="CR67" t="n">
-        <v>10.35</v>
+      <c r="CQ67" t="inlineStr">
+        <is>
+          <t>10.59</t>
+        </is>
+      </c>
+      <c r="CR67" t="inlineStr">
+        <is>
+          <t>10.35</t>
+        </is>
       </c>
       <c r="CS67" t="inlineStr">
         <is>
@@ -66107,7 +66371,7 @@
       </c>
       <c r="DQ67" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR67" t="inlineStr">
@@ -66719,62 +66983,62 @@
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR68" t="inlineStr">
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT68" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
@@ -66973,11 +67237,15 @@
           <t>10.705</t>
         </is>
       </c>
-      <c r="CQ68" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="CR68" t="n">
-        <v>10.33</v>
+      <c r="CQ68" t="inlineStr">
+        <is>
+          <t>10.55</t>
+        </is>
+      </c>
+      <c r="CR68" t="inlineStr">
+        <is>
+          <t>10.33</t>
+        </is>
       </c>
       <c r="CS68" t="inlineStr">
         <is>
@@ -67093,7 +67361,7 @@
       </c>
       <c r="DQ68" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR68" t="inlineStr">
@@ -67705,62 +67973,62 @@
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR69" t="inlineStr">
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS69" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT69" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV69" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
@@ -67959,11 +68227,15 @@
           <t>10.685</t>
         </is>
       </c>
-      <c r="CQ69" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="CR69" t="n">
-        <v>10.33</v>
+      <c r="CQ69" t="inlineStr">
+        <is>
+          <t>10.53</t>
+        </is>
+      </c>
+      <c r="CR69" t="inlineStr">
+        <is>
+          <t>10.33</t>
+        </is>
       </c>
       <c r="CS69" t="inlineStr">
         <is>
@@ -68079,7 +68351,7 @@
       </c>
       <c r="DQ69" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR69" t="inlineStr">
@@ -68691,32 +68963,32 @@
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT70" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
@@ -68731,22 +69003,22 @@
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
@@ -68945,11 +69217,15 @@
           <t>10.63</t>
         </is>
       </c>
-      <c r="CQ70" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="CR70" t="n">
-        <v>10.33</v>
+      <c r="CQ70" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="CR70" t="inlineStr">
+        <is>
+          <t>10.33</t>
+        </is>
       </c>
       <c r="CS70" t="inlineStr">
         <is>
@@ -69065,7 +69341,7 @@
       </c>
       <c r="DQ70" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR70" t="inlineStr">
@@ -69682,57 +69958,57 @@
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV71" t="inlineStr">
+      <c r="AW71" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW71" t="inlineStr">
+      <c r="AX71" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
@@ -69931,11 +70207,15 @@
           <t>10.545</t>
         </is>
       </c>
-      <c r="CQ71" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="CR71" t="n">
-        <v>10.31</v>
+      <c r="CQ71" t="inlineStr">
+        <is>
+          <t>10.44</t>
+        </is>
+      </c>
+      <c r="CR71" t="inlineStr">
+        <is>
+          <t>10.31</t>
+        </is>
       </c>
       <c r="CS71" t="inlineStr">
         <is>
@@ -70051,7 +70331,7 @@
       </c>
       <c r="DQ71" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR71" t="inlineStr">
@@ -70663,62 +70943,62 @@
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV72" t="inlineStr">
+      <c r="AW72" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW72" t="inlineStr">
+      <c r="AX72" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
@@ -70917,11 +71197,15 @@
           <t>10.495</t>
         </is>
       </c>
-      <c r="CQ72" t="n">
-        <v>10.42</v>
-      </c>
-      <c r="CR72" t="n">
-        <v>10.3</v>
+      <c r="CQ72" t="inlineStr">
+        <is>
+          <t>10.42</t>
+        </is>
+      </c>
+      <c r="CR72" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
       </c>
       <c r="CS72" t="inlineStr">
         <is>
@@ -71037,7 +71321,7 @@
       </c>
       <c r="DQ72" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR72" t="inlineStr">
@@ -71654,17 +71938,17 @@
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
@@ -71674,37 +71958,37 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW73" t="inlineStr">
+      <c r="AX73" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
@@ -71903,11 +72187,15 @@
           <t>10.44</t>
         </is>
       </c>
-      <c r="CQ73" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="CR73" t="n">
-        <v>10.3</v>
+      <c r="CQ73" t="inlineStr">
+        <is>
+          <t>10.41</t>
+        </is>
+      </c>
+      <c r="CR73" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
       </c>
       <c r="CS73" t="inlineStr">
         <is>
@@ -72023,7 +72311,7 @@
       </c>
       <c r="DQ73" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR73" t="inlineStr">
@@ -72655,12 +72943,12 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
@@ -72675,22 +72963,22 @@
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
@@ -72889,11 +73177,15 @@
           <t>27.82999999999999</t>
         </is>
       </c>
-      <c r="CQ74" t="n">
-        <v>27.19</v>
-      </c>
-      <c r="CR74" t="n">
-        <v>26.26</v>
+      <c r="CQ74" t="inlineStr">
+        <is>
+          <t>27.19</t>
+        </is>
+      </c>
+      <c r="CR74" t="inlineStr">
+        <is>
+          <t>26.26</t>
+        </is>
       </c>
       <c r="CS74" t="inlineStr">
         <is>
@@ -73009,7 +73301,7 @@
       </c>
       <c r="DQ74" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR74" t="inlineStr">
@@ -73641,12 +73933,12 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
@@ -73661,22 +73953,22 @@
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
@@ -73875,11 +74167,15 @@
           <t>27.7</t>
         </is>
       </c>
-      <c r="CQ75" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="CR75" t="n">
-        <v>26.18</v>
+      <c r="CQ75" t="inlineStr">
+        <is>
+          <t>27.2</t>
+        </is>
+      </c>
+      <c r="CR75" t="inlineStr">
+        <is>
+          <t>26.18</t>
+        </is>
       </c>
       <c r="CS75" t="inlineStr">
         <is>
@@ -73995,7 +74291,7 @@
       </c>
       <c r="DQ75" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR75" t="inlineStr">
@@ -74627,12 +74923,12 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
@@ -74647,22 +74943,22 @@
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
@@ -74861,11 +75157,15 @@
           <t>27.48</t>
         </is>
       </c>
-      <c r="CQ76" t="n">
-        <v>27.24</v>
-      </c>
-      <c r="CR76" t="n">
-        <v>26.1</v>
+      <c r="CQ76" t="inlineStr">
+        <is>
+          <t>27.24</t>
+        </is>
+      </c>
+      <c r="CR76" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
       </c>
       <c r="CS76" t="inlineStr">
         <is>
@@ -74981,7 +75281,7 @@
       </c>
       <c r="DQ76" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR76" t="inlineStr">
@@ -75618,7 +75918,7 @@
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
@@ -75633,22 +75933,22 @@
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
@@ -75847,11 +76147,15 @@
           <t>27.21</t>
         </is>
       </c>
-      <c r="CQ77" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="CR77" t="n">
-        <v>26</v>
+      <c r="CQ77" t="inlineStr">
+        <is>
+          <t>27.25</t>
+        </is>
+      </c>
+      <c r="CR77" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="CS77" t="inlineStr">
         <is>
@@ -76604,7 +76908,7 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
@@ -76619,22 +76923,22 @@
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
@@ -76833,11 +77137,15 @@
           <t>27.045</t>
         </is>
       </c>
-      <c r="CQ78" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="CR78" t="n">
-        <v>25.92</v>
+      <c r="CQ78" t="inlineStr">
+        <is>
+          <t>27.29</t>
+        </is>
+      </c>
+      <c r="CR78" t="inlineStr">
+        <is>
+          <t>25.92</t>
+        </is>
       </c>
       <c r="CS78" t="inlineStr">
         <is>
@@ -77590,7 +77898,7 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
@@ -77605,22 +77913,22 @@
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
@@ -77819,11 +78127,15 @@
           <t>26.85</t>
         </is>
       </c>
-      <c r="CQ79" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>25.85</v>
+      <c r="CQ79" t="inlineStr">
+        <is>
+          <t>27.29</t>
+        </is>
+      </c>
+      <c r="CR79" t="inlineStr">
+        <is>
+          <t>25.85</t>
+        </is>
       </c>
       <c r="CS79" t="inlineStr">
         <is>
@@ -78576,7 +78888,7 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
@@ -78591,22 +78903,22 @@
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
@@ -78805,11 +79117,15 @@
           <t>26.71</t>
         </is>
       </c>
-      <c r="CQ80" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>25.81</v>
+      <c r="CQ80" t="inlineStr">
+        <is>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="CR80" t="inlineStr">
+        <is>
+          <t>25.81</t>
+        </is>
       </c>
       <c r="CS80" t="inlineStr">
         <is>
@@ -79562,7 +79878,7 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
@@ -79577,22 +79893,22 @@
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
@@ -79791,11 +80107,15 @@
           <t>26.55</t>
         </is>
       </c>
-      <c r="CQ81" t="n">
-        <v>27.34</v>
-      </c>
-      <c r="CR81" t="n">
-        <v>25.76</v>
+      <c r="CQ81" t="inlineStr">
+        <is>
+          <t>27.34</t>
+        </is>
+      </c>
+      <c r="CR81" t="inlineStr">
+        <is>
+          <t>25.76</t>
+        </is>
       </c>
       <c r="CS81" t="inlineStr">
         <is>
@@ -80548,7 +80868,7 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
@@ -80563,22 +80883,22 @@
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
@@ -80777,11 +81097,15 @@
           <t>26.51</t>
         </is>
       </c>
-      <c r="CQ82" t="n">
-        <v>27.37</v>
-      </c>
-      <c r="CR82" t="n">
-        <v>25.67</v>
+      <c r="CQ82" t="inlineStr">
+        <is>
+          <t>27.37</t>
+        </is>
+      </c>
+      <c r="CR82" t="inlineStr">
+        <is>
+          <t>25.67</t>
+        </is>
       </c>
       <c r="CS82" t="inlineStr">
         <is>
@@ -81534,7 +81858,7 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
@@ -81549,7 +81873,7 @@
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
@@ -81763,11 +82087,15 @@
           <t>16.85</t>
         </is>
       </c>
-      <c r="CQ83" t="n">
-        <v>17.39</v>
-      </c>
-      <c r="CR83" t="n">
-        <v>18.25</v>
+      <c r="CQ83" t="inlineStr">
+        <is>
+          <t>17.39</t>
+        </is>
+      </c>
+      <c r="CR83" t="inlineStr">
+        <is>
+          <t>18.25</t>
+        </is>
       </c>
       <c r="CS83" t="inlineStr">
         <is>
@@ -82520,7 +82848,7 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
@@ -82535,7 +82863,7 @@
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
@@ -82749,11 +83077,15 @@
           <t>16.96</t>
         </is>
       </c>
-      <c r="CQ84" t="n">
-        <v>17.48</v>
-      </c>
-      <c r="CR84" t="n">
-        <v>18.3</v>
+      <c r="CQ84" t="inlineStr">
+        <is>
+          <t>17.48</t>
+        </is>
+      </c>
+      <c r="CR84" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
       </c>
       <c r="CS84" t="inlineStr">
         <is>
@@ -83506,7 +83838,7 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
@@ -83521,7 +83853,7 @@
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
@@ -83735,11 +84067,15 @@
           <t>17.055</t>
         </is>
       </c>
-      <c r="CQ85" t="n">
-        <v>17.56</v>
-      </c>
-      <c r="CR85" t="n">
-        <v>18.35</v>
+      <c r="CQ85" t="inlineStr">
+        <is>
+          <t>17.56</t>
+        </is>
+      </c>
+      <c r="CR85" t="inlineStr">
+        <is>
+          <t>18.35</t>
+        </is>
       </c>
       <c r="CS85" t="inlineStr">
         <is>
@@ -84492,7 +84828,7 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
@@ -84507,7 +84843,7 @@
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
@@ -84522,7 +84858,7 @@
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
@@ -84721,11 +85057,15 @@
           <t>17.19</t>
         </is>
       </c>
-      <c r="CQ86" t="n">
-        <v>17.66</v>
-      </c>
-      <c r="CR86" t="n">
-        <v>18.39</v>
+      <c r="CQ86" t="inlineStr">
+        <is>
+          <t>17.66</t>
+        </is>
+      </c>
+      <c r="CR86" t="inlineStr">
+        <is>
+          <t>18.39</t>
+        </is>
       </c>
       <c r="CS86" t="inlineStr">
         <is>
@@ -85478,7 +85818,7 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
@@ -85493,7 +85833,7 @@
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
@@ -85508,7 +85848,7 @@
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
@@ -85707,11 +86047,15 @@
           <t>17.355</t>
         </is>
       </c>
-      <c r="CQ87" t="n">
-        <v>17.77</v>
-      </c>
-      <c r="CR87" t="n">
-        <v>18.44</v>
+      <c r="CQ87" t="inlineStr">
+        <is>
+          <t>17.77</t>
+        </is>
+      </c>
+      <c r="CR87" t="inlineStr">
+        <is>
+          <t>18.44</t>
+        </is>
       </c>
       <c r="CS87" t="inlineStr">
         <is>
@@ -86464,7 +86808,7 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
@@ -86479,7 +86823,7 @@
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
@@ -86494,7 +86838,7 @@
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
@@ -86693,11 +87037,15 @@
           <t>17.51</t>
         </is>
       </c>
-      <c r="CQ88" t="n">
-        <v>17.88</v>
-      </c>
-      <c r="CR88" t="n">
-        <v>18.49</v>
+      <c r="CQ88" t="inlineStr">
+        <is>
+          <t>17.88</t>
+        </is>
+      </c>
+      <c r="CR88" t="inlineStr">
+        <is>
+          <t>18.49</t>
+        </is>
       </c>
       <c r="CS88" t="inlineStr">
         <is>
@@ -87450,7 +87798,7 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
@@ -87465,7 +87813,7 @@
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
@@ -87480,7 +87828,7 @@
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
@@ -87679,11 +88027,15 @@
           <t>17.615</t>
         </is>
       </c>
-      <c r="CQ89" t="n">
-        <v>17.98</v>
-      </c>
-      <c r="CR89" t="n">
-        <v>18.54</v>
+      <c r="CQ89" t="inlineStr">
+        <is>
+          <t>17.98</t>
+        </is>
+      </c>
+      <c r="CR89" t="inlineStr">
+        <is>
+          <t>18.54</t>
+        </is>
       </c>
       <c r="CS89" t="inlineStr">
         <is>
@@ -88436,7 +88788,7 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
@@ -88451,7 +88803,7 @@
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
@@ -88466,7 +88818,7 @@
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
@@ -88665,11 +89017,15 @@
           <t>17.73</t>
         </is>
       </c>
-      <c r="CQ90" t="n">
-        <v>18.08</v>
-      </c>
-      <c r="CR90" t="n">
-        <v>18.58</v>
+      <c r="CQ90" t="inlineStr">
+        <is>
+          <t>18.08</t>
+        </is>
+      </c>
+      <c r="CR90" t="inlineStr">
+        <is>
+          <t>18.58</t>
+        </is>
       </c>
       <c r="CS90" t="inlineStr">
         <is>
@@ -89422,7 +89778,7 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
@@ -89437,7 +89793,7 @@
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
@@ -89452,7 +89808,7 @@
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
@@ -89651,11 +90007,15 @@
           <t>17.815</t>
         </is>
       </c>
-      <c r="CQ91" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="CR91" t="n">
-        <v>18.62</v>
+      <c r="CQ91" t="inlineStr">
+        <is>
+          <t>18.16</t>
+        </is>
+      </c>
+      <c r="CR91" t="inlineStr">
+        <is>
+          <t>18.62</t>
+        </is>
       </c>
       <c r="CS91" t="inlineStr">
         <is>
@@ -90408,7 +90768,7 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
@@ -90423,7 +90783,7 @@
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
@@ -90438,7 +90798,7 @@
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
@@ -90637,11 +90997,15 @@
           <t>29.995</t>
         </is>
       </c>
-      <c r="CQ92" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="CR92" t="n">
-        <v>31.94</v>
+      <c r="CQ92" t="inlineStr">
+        <is>
+          <t>30.3</t>
+        </is>
+      </c>
+      <c r="CR92" t="inlineStr">
+        <is>
+          <t>31.94</t>
+        </is>
       </c>
       <c r="CS92" t="inlineStr">
         <is>
@@ -91394,7 +91758,7 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
@@ -91409,7 +91773,7 @@
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
@@ -91424,7 +91788,7 @@
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
@@ -91623,11 +91987,15 @@
           <t>30.05</t>
         </is>
       </c>
-      <c r="CQ93" t="n">
-        <v>30.42</v>
-      </c>
-      <c r="CR93" t="n">
-        <v>32.02</v>
+      <c r="CQ93" t="inlineStr">
+        <is>
+          <t>30.42</t>
+        </is>
+      </c>
+      <c r="CR93" t="inlineStr">
+        <is>
+          <t>32.02</t>
+        </is>
       </c>
       <c r="CS93" t="inlineStr">
         <is>
@@ -92380,7 +92748,7 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
@@ -92395,7 +92763,7 @@
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
@@ -92410,7 +92778,7 @@
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
@@ -92609,11 +92977,15 @@
           <t>30.085</t>
         </is>
       </c>
-      <c r="CQ94" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="CR94" t="n">
-        <v>32.11</v>
+      <c r="CQ94" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="CR94" t="inlineStr">
+        <is>
+          <t>32.11</t>
+        </is>
       </c>
       <c r="CS94" t="inlineStr">
         <is>
@@ -93366,7 +93738,7 @@
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
@@ -93381,7 +93753,7 @@
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
@@ -93396,7 +93768,7 @@
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
@@ -93595,11 +93967,15 @@
           <t>30.11</t>
         </is>
       </c>
-      <c r="CQ95" t="n">
-        <v>30.57</v>
-      </c>
-      <c r="CR95" t="n">
-        <v>32.18</v>
+      <c r="CQ95" t="inlineStr">
+        <is>
+          <t>30.57</t>
+        </is>
+      </c>
+      <c r="CR95" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
       </c>
       <c r="CS95" t="inlineStr">
         <is>
@@ -94352,7 +94728,7 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
@@ -94367,7 +94743,7 @@
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
@@ -94382,7 +94758,7 @@
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
@@ -94581,11 +94957,15 @@
           <t>30.15499999999999</t>
         </is>
       </c>
-      <c r="CQ96" t="n">
-        <v>30.67</v>
-      </c>
-      <c r="CR96" t="n">
-        <v>32.26</v>
+      <c r="CQ96" t="inlineStr">
+        <is>
+          <t>30.67</t>
+        </is>
+      </c>
+      <c r="CR96" t="inlineStr">
+        <is>
+          <t>32.26</t>
+        </is>
       </c>
       <c r="CS96" t="inlineStr">
         <is>
@@ -95338,7 +95718,7 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
@@ -95353,7 +95733,7 @@
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
@@ -95368,7 +95748,7 @@
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
@@ -95567,11 +95947,15 @@
           <t>30.21</t>
         </is>
       </c>
-      <c r="CQ97" t="n">
-        <v>30.82</v>
-      </c>
-      <c r="CR97" t="n">
-        <v>32.36</v>
+      <c r="CQ97" t="inlineStr">
+        <is>
+          <t>30.82</t>
+        </is>
+      </c>
+      <c r="CR97" t="inlineStr">
+        <is>
+          <t>32.36</t>
+        </is>
       </c>
       <c r="CS97" t="inlineStr">
         <is>
@@ -96324,7 +96708,7 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
@@ -96339,7 +96723,7 @@
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
@@ -96354,7 +96738,7 @@
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
@@ -96553,11 +96937,15 @@
           <t>30.29</t>
         </is>
       </c>
-      <c r="CQ98" t="n">
-        <v>30.97</v>
-      </c>
-      <c r="CR98" t="n">
-        <v>32.44</v>
+      <c r="CQ98" t="inlineStr">
+        <is>
+          <t>30.97</t>
+        </is>
+      </c>
+      <c r="CR98" t="inlineStr">
+        <is>
+          <t>32.44</t>
+        </is>
       </c>
       <c r="CS98" t="inlineStr">
         <is>
@@ -97310,7 +97698,7 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
@@ -97325,7 +97713,7 @@
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
@@ -97340,7 +97728,7 @@
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
@@ -97539,11 +97927,15 @@
           <t>30.36</t>
         </is>
       </c>
-      <c r="CQ99" t="n">
-        <v>31.13</v>
-      </c>
-      <c r="CR99" t="n">
-        <v>32.52</v>
+      <c r="CQ99" t="inlineStr">
+        <is>
+          <t>31.13</t>
+        </is>
+      </c>
+      <c r="CR99" t="inlineStr">
+        <is>
+          <t>32.52</t>
+        </is>
       </c>
       <c r="CS99" t="inlineStr">
         <is>
@@ -98296,7 +98688,7 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
@@ -98311,7 +98703,7 @@
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
@@ -98326,7 +98718,7 @@
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
@@ -98525,11 +98917,15 @@
           <t>30.42</t>
         </is>
       </c>
-      <c r="CQ100" t="n">
-        <v>31.28</v>
-      </c>
-      <c r="CR100" t="n">
-        <v>32.6</v>
+      <c r="CQ100" t="inlineStr">
+        <is>
+          <t>31.28</t>
+        </is>
+      </c>
+      <c r="CR100" t="inlineStr">
+        <is>
+          <t>32.6</t>
+        </is>
       </c>
       <c r="CS100" t="inlineStr">
         <is>
